--- a/docs/podskazki-kartochki-zdaniya.xlsx
+++ b/docs/podskazki-kartochki-zdaniya.xlsx
@@ -849,12 +849,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>По фото с осмотра. Назначение по техпаспорту — ориентир: там часто пусто, «здание» или неверно</t>
+          <t>По фото с осмотра</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>По фото с осмотра. Назначение по техпаспорту — ориентир: там часто пусто, «здание» или неверно. От вида зависят признаки класса и доп. параметры</t>
+          <t>По фото с осмотра. От вида зависят признаки класса и доп. параметры</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Слова пользователя 24.09.2026</t>
+          <t>Решение пользователя 23.09.2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Из техпаспорта. Здание достраивали — годы частей через запятую. Даты последующих обследований в техпаспорте — не год постройки</t>
+          <t>Из техпаспорта. Здание достраивали — годы частей через запятую</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -950,11 +950,7 @@
           <t>всплывающая</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Закон КР о регистрации прав на недвижимость, ст. 25-1 (текущее обследование вносится в тот же техпаспорт)</t>
-        </is>
-      </c>
+      <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1210,7 +1206,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Как записано в техпаспорте, дословно. В техпаспорте пусто — оставить пустым</t>
+          <t>Как записано в техпаспорте, дословно</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
